--- a/upload/report/test_hiraoka5.xlsx
+++ b/upload/report/test_hiraoka5.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="190">
   <si>
     <t>Purchase order items PDF to Excel</t>
   </si>
@@ -23,7 +23,16 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-02 19:27:53</t>
+    <t>2024-04-03 11:34:49</t>
+  </si>
+  <si>
+    <t>Customer</t>
+  </si>
+  <si>
+    <t>Address</t>
+  </si>
+  <si>
+    <t>#Order</t>
   </si>
   <si>
     <t>Num</t>
@@ -44,7 +53,16 @@
     <t>Total</t>
   </si>
   <si>
-    <t>Product</t>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>IMPORTACIONES HIRAOKA S.A.C.</t>
+  </si>
+  <si>
+    <t>CALLE 5, MZ. D-1, LOTE 5 - COOP., LAS VER VILLA EL SALVADOR</t>
+  </si>
+  <si>
+    <t>132676</t>
   </si>
   <si>
     <t>1</t>
@@ -485,7 +503,88 @@
     <t>55</t>
   </si>
   <si>
-    <t xml:space="preserve"> 363.6800 20,002.40HORNO MICROONDA LG - MH-6536GIS</t>
+    <t>363.6800</t>
+  </si>
+  <si>
+    <t>20,002.40</t>
+  </si>
+  <si>
+    <t>HORNO MICROONDA LG - MH-6536GIS</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>131013</t>
+  </si>
+  <si>
+    <t>244</t>
+  </si>
+  <si>
+    <t>349.1000</t>
+  </si>
+  <si>
+    <t>85,180.40</t>
+  </si>
+  <si>
+    <t>HORNO MICROONDA LG - MH7032JAS</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>109948</t>
+  </si>
+  <si>
+    <t>509.4400</t>
+  </si>
+  <si>
+    <t>12,736.00</t>
+  </si>
+  <si>
+    <t>HORNO MICROONDA LG - MH-8296DIR</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>108259</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>327.2400</t>
+  </si>
+  <si>
+    <t>16,362.00</t>
+  </si>
+  <si>
+    <t>HORNO MICROONDA LG - MS-2536GIS</t>
+  </si>
+  <si>
+    <t>109801</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>12,218.50</t>
+  </si>
+  <si>
+    <t>HORNO MICROONDA LG - MS-2596DIR</t>
+  </si>
+  <si>
+    <t>109800</t>
+  </si>
+  <si>
+    <t>436.5600</t>
+  </si>
+  <si>
+    <t>4,365.60</t>
+  </si>
+  <si>
+    <t>HORNO MICROONDA LG - MS-4296DIR</t>
   </si>
 </sst>
 </file>
@@ -825,15 +924,15 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -841,7 +940,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -863,622 +962,1038 @@
       <c r="G4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:7">
+      <c r="H4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" t="s">
+        <v>11</v>
+      </c>
+      <c r="J4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" t="s">
+        <v>26</v>
+      </c>
+      <c r="I6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" t="s">
+        <v>33</v>
+      </c>
+      <c r="J7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" t="s">
+        <v>37</v>
+      </c>
+      <c r="H8" t="s">
+        <v>38</v>
+      </c>
+      <c r="I8" t="s">
+        <v>39</v>
+      </c>
+      <c r="J8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" t="s">
+        <v>43</v>
+      </c>
+      <c r="H9" t="s">
+        <v>44</v>
+      </c>
+      <c r="I9" t="s">
+        <v>45</v>
+      </c>
+      <c r="J9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" t="s">
+        <v>48</v>
+      </c>
+      <c r="F10" t="s">
+        <v>18</v>
+      </c>
+      <c r="G10" t="s">
+        <v>49</v>
+      </c>
+      <c r="H10" t="s">
+        <v>50</v>
+      </c>
+      <c r="I10" t="s">
+        <v>51</v>
+      </c>
+      <c r="J10" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" t="s">
+        <v>53</v>
+      </c>
+      <c r="E11" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" t="s">
+        <v>55</v>
+      </c>
+      <c r="H11" t="s">
+        <v>56</v>
+      </c>
+      <c r="I11" t="s">
+        <v>57</v>
+      </c>
+      <c r="J11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E12" t="s">
+        <v>60</v>
+      </c>
+      <c r="F12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G12" t="s">
+        <v>61</v>
+      </c>
+      <c r="H12" t="s">
+        <v>62</v>
+      </c>
+      <c r="I12" t="s">
+        <v>63</v>
+      </c>
+      <c r="J12" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" t="s">
+        <v>65</v>
+      </c>
+      <c r="E13" t="s">
+        <v>66</v>
+      </c>
+      <c r="F13" t="s">
+        <v>18</v>
+      </c>
+      <c r="G13" t="s">
+        <v>67</v>
+      </c>
+      <c r="H13" t="s">
+        <v>68</v>
+      </c>
+      <c r="I13" t="s">
+        <v>69</v>
+      </c>
+      <c r="J13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" t="s">
+        <v>71</v>
+      </c>
+      <c r="E14" t="s">
+        <v>72</v>
+      </c>
+      <c r="F14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G14" t="s">
+        <v>73</v>
+      </c>
+      <c r="H14" t="s">
+        <v>74</v>
+      </c>
+      <c r="I14" t="s">
+        <v>75</v>
+      </c>
+      <c r="J14" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E15" t="s">
+        <v>78</v>
+      </c>
+      <c r="F15" t="s">
+        <v>18</v>
+      </c>
+      <c r="G15" t="s">
+        <v>47</v>
+      </c>
+      <c r="H15" t="s">
+        <v>79</v>
+      </c>
+      <c r="I15" t="s">
+        <v>80</v>
+      </c>
+      <c r="J15" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" t="s">
+        <v>82</v>
+      </c>
+      <c r="E16" t="s">
+        <v>83</v>
+      </c>
+      <c r="F16" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16" t="s">
+        <v>84</v>
+      </c>
+      <c r="H16" t="s">
+        <v>85</v>
+      </c>
+      <c r="I16" t="s">
+        <v>86</v>
+      </c>
+      <c r="J16" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" t="s">
+        <v>88</v>
+      </c>
+      <c r="E17" t="s">
+        <v>89</v>
+      </c>
+      <c r="F17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" t="s">
+        <v>71</v>
+      </c>
+      <c r="H17" t="s">
+        <v>90</v>
+      </c>
+      <c r="I17" t="s">
+        <v>91</v>
+      </c>
+      <c r="J17" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" t="s">
+        <v>93</v>
+      </c>
+      <c r="E18" t="s">
+        <v>94</v>
+      </c>
+      <c r="F18" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" t="s">
+        <v>95</v>
+      </c>
+      <c r="H18" t="s">
+        <v>96</v>
+      </c>
+      <c r="I18" t="s">
+        <v>97</v>
+      </c>
+      <c r="J18" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" t="s">
+        <v>99</v>
+      </c>
+      <c r="E19" t="s">
+        <v>100</v>
+      </c>
+      <c r="F19" t="s">
+        <v>18</v>
+      </c>
+      <c r="G19" t="s">
+        <v>84</v>
+      </c>
+      <c r="H19" t="s">
+        <v>101</v>
+      </c>
+      <c r="I19" t="s">
+        <v>102</v>
+      </c>
+      <c r="J19" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" t="s">
+        <v>67</v>
+      </c>
+      <c r="E20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G20" t="s">
+        <v>99</v>
+      </c>
+      <c r="H20" t="s">
+        <v>105</v>
+      </c>
+      <c r="I20" t="s">
+        <v>106</v>
+      </c>
+      <c r="J20" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" t="s">
+        <v>108</v>
+      </c>
+      <c r="E21" t="s">
+        <v>109</v>
+      </c>
+      <c r="F21" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" t="s">
+        <v>110</v>
+      </c>
+      <c r="H21" t="s">
+        <v>111</v>
+      </c>
+      <c r="I21" t="s">
+        <v>112</v>
+      </c>
+      <c r="J21" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" t="s">
+        <v>13</v>
+      </c>
+      <c r="B22" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" t="s">
+        <v>114</v>
+      </c>
+      <c r="E22" t="s">
+        <v>115</v>
+      </c>
+      <c r="F22" t="s">
+        <v>18</v>
+      </c>
+      <c r="G22" t="s">
+        <v>116</v>
+      </c>
+      <c r="H22" t="s">
+        <v>117</v>
+      </c>
+      <c r="I22" t="s">
+        <v>118</v>
+      </c>
+      <c r="J22" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" t="s">
+        <v>13</v>
+      </c>
+      <c r="B23" t="s">
+        <v>14</v>
+      </c>
+      <c r="C23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" t="s">
+        <v>120</v>
+      </c>
+      <c r="E23" t="s">
+        <v>121</v>
+      </c>
+      <c r="F23" t="s">
+        <v>18</v>
+      </c>
+      <c r="G23" t="s">
+        <v>82</v>
+      </c>
+      <c r="H23" t="s">
+        <v>38</v>
+      </c>
+      <c r="I23" t="s">
+        <v>122</v>
+      </c>
+      <c r="J23" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" t="s">
+        <v>13</v>
+      </c>
+      <c r="B24" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D24" t="s">
+        <v>124</v>
+      </c>
+      <c r="E24" t="s">
+        <v>125</v>
+      </c>
+      <c r="F24" t="s">
+        <v>18</v>
+      </c>
+      <c r="G24" t="s">
+        <v>126</v>
+      </c>
+      <c r="H24" t="s">
+        <v>127</v>
+      </c>
+      <c r="I24" t="s">
+        <v>128</v>
+      </c>
+      <c r="J24" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" t="s">
+        <v>13</v>
+      </c>
+      <c r="B25" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" t="s">
         <v>19</v>
       </c>
-      <c r="E6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" t="s">
-        <v>21</v>
-      </c>
-      <c r="G6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" t="s">
-        <v>31</v>
-      </c>
-      <c r="E8" t="s">
-        <v>32</v>
-      </c>
-      <c r="F8" t="s">
-        <v>33</v>
-      </c>
-      <c r="G8" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" t="s">
-        <v>35</v>
-      </c>
-      <c r="B9" t="s">
-        <v>36</v>
-      </c>
-      <c r="C9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" t="s">
-        <v>37</v>
-      </c>
-      <c r="E9" t="s">
-        <v>38</v>
-      </c>
-      <c r="F9" t="s">
-        <v>39</v>
-      </c>
-      <c r="G9" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" t="s">
+      <c r="E25" t="s">
+        <v>130</v>
+      </c>
+      <c r="F25" t="s">
+        <v>18</v>
+      </c>
+      <c r="G25" t="s">
+        <v>99</v>
+      </c>
+      <c r="H25" t="s">
+        <v>131</v>
+      </c>
+      <c r="I25" t="s">
+        <v>132</v>
+      </c>
+      <c r="J25" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" t="s">
+        <v>13</v>
+      </c>
+      <c r="B26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C26" t="s">
+        <v>15</v>
+      </c>
+      <c r="D26" t="s">
+        <v>134</v>
+      </c>
+      <c r="E26" t="s">
+        <v>135</v>
+      </c>
+      <c r="F26" t="s">
+        <v>18</v>
+      </c>
+      <c r="G26" t="s">
+        <v>136</v>
+      </c>
+      <c r="H26" t="s">
+        <v>137</v>
+      </c>
+      <c r="I26" t="s">
+        <v>138</v>
+      </c>
+      <c r="J26" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" t="s">
+        <v>13</v>
+      </c>
+      <c r="B27" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27" t="s">
+        <v>15</v>
+      </c>
+      <c r="D27" t="s">
+        <v>140</v>
+      </c>
+      <c r="E27" t="s">
+        <v>141</v>
+      </c>
+      <c r="F27" t="s">
+        <v>18</v>
+      </c>
+      <c r="G27" t="s">
+        <v>71</v>
+      </c>
+      <c r="H27" t="s">
+        <v>142</v>
+      </c>
+      <c r="I27" t="s">
+        <v>143</v>
+      </c>
+      <c r="J27" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" t="s">
+        <v>13</v>
+      </c>
+      <c r="B28" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28" t="s">
+        <v>15</v>
+      </c>
+      <c r="D28" t="s">
+        <v>145</v>
+      </c>
+      <c r="E28" t="s">
+        <v>146</v>
+      </c>
+      <c r="F28" t="s">
+        <v>18</v>
+      </c>
+      <c r="G28" t="s">
         <v>41</v>
       </c>
-      <c r="B10" t="s">
-        <v>42</v>
-      </c>
-      <c r="C10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E10" t="s">
-        <v>44</v>
-      </c>
-      <c r="F10" t="s">
-        <v>45</v>
-      </c>
-      <c r="G10" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" t="s">
-        <v>47</v>
-      </c>
-      <c r="B11" t="s">
-        <v>48</v>
-      </c>
-      <c r="C11" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" t="s">
-        <v>49</v>
-      </c>
-      <c r="E11" t="s">
-        <v>50</v>
-      </c>
-      <c r="F11" t="s">
-        <v>51</v>
-      </c>
-      <c r="G11" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" t="s">
-        <v>53</v>
-      </c>
-      <c r="B12" t="s">
-        <v>54</v>
-      </c>
-      <c r="C12" t="s">
-        <v>12</v>
-      </c>
-      <c r="D12" t="s">
-        <v>55</v>
-      </c>
-      <c r="E12" t="s">
-        <v>56</v>
-      </c>
-      <c r="F12" t="s">
-        <v>57</v>
-      </c>
-      <c r="G12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" t="s">
-        <v>59</v>
-      </c>
-      <c r="B13" t="s">
-        <v>60</v>
-      </c>
-      <c r="C13" t="s">
-        <v>12</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="H28" t="s">
+        <v>147</v>
+      </c>
+      <c r="I28" t="s">
+        <v>148</v>
+      </c>
+      <c r="J28" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" t="s">
+        <v>13</v>
+      </c>
+      <c r="B29" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" t="s">
+        <v>15</v>
+      </c>
+      <c r="D29" t="s">
+        <v>150</v>
+      </c>
+      <c r="E29" t="s">
+        <v>151</v>
+      </c>
+      <c r="F29" t="s">
+        <v>18</v>
+      </c>
+      <c r="G29" t="s">
+        <v>99</v>
+      </c>
+      <c r="H29" t="s">
+        <v>152</v>
+      </c>
+      <c r="I29" t="s">
+        <v>153</v>
+      </c>
+      <c r="J29" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" t="s">
+        <v>13</v>
+      </c>
+      <c r="B30" t="s">
+        <v>14</v>
+      </c>
+      <c r="C30" t="s">
+        <v>15</v>
+      </c>
+      <c r="D30" t="s">
+        <v>155</v>
+      </c>
+      <c r="E30" t="s">
+        <v>156</v>
+      </c>
+      <c r="F30" t="s">
+        <v>18</v>
+      </c>
+      <c r="G30" t="s">
+        <v>99</v>
+      </c>
+      <c r="H30" t="s">
+        <v>157</v>
+      </c>
+      <c r="I30" t="s">
+        <v>158</v>
+      </c>
+      <c r="J30" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" t="s">
+        <v>13</v>
+      </c>
+      <c r="B31" t="s">
+        <v>14</v>
+      </c>
+      <c r="C31" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" t="s">
         <v>61</v>
       </c>
-      <c r="E13" t="s">
-        <v>62</v>
-      </c>
-      <c r="F13" t="s">
-        <v>63</v>
-      </c>
-      <c r="G13" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" t="s">
-        <v>65</v>
-      </c>
-      <c r="B14" t="s">
-        <v>66</v>
-      </c>
-      <c r="C14" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" t="s">
-        <v>67</v>
-      </c>
-      <c r="E14" t="s">
-        <v>68</v>
-      </c>
-      <c r="F14" t="s">
-        <v>69</v>
-      </c>
-      <c r="G14" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" t="s">
+      <c r="E31" t="s">
+        <v>160</v>
+      </c>
+      <c r="F31" t="s">
+        <v>18</v>
+      </c>
+      <c r="G31" t="s">
+        <v>161</v>
+      </c>
+      <c r="H31" t="s">
+        <v>162</v>
+      </c>
+      <c r="I31" t="s">
+        <v>163</v>
+      </c>
+      <c r="J31" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" t="s">
+        <v>13</v>
+      </c>
+      <c r="B32" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" t="s">
+        <v>15</v>
+      </c>
+      <c r="D32" t="s">
+        <v>165</v>
+      </c>
+      <c r="E32" t="s">
+        <v>166</v>
+      </c>
+      <c r="F32" t="s">
+        <v>18</v>
+      </c>
+      <c r="G32" t="s">
+        <v>167</v>
+      </c>
+      <c r="H32" t="s">
+        <v>168</v>
+      </c>
+      <c r="I32" t="s">
+        <v>169</v>
+      </c>
+      <c r="J32" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33" t="s">
+        <v>13</v>
+      </c>
+      <c r="B33" t="s">
+        <v>14</v>
+      </c>
+      <c r="C33" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" t="s">
+        <v>171</v>
+      </c>
+      <c r="E33" t="s">
+        <v>172</v>
+      </c>
+      <c r="F33" t="s">
+        <v>18</v>
+      </c>
+      <c r="G33" t="s">
+        <v>150</v>
+      </c>
+      <c r="H33" t="s">
+        <v>173</v>
+      </c>
+      <c r="I33" t="s">
+        <v>174</v>
+      </c>
+      <c r="J33" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34" t="s">
+        <v>13</v>
+      </c>
+      <c r="B34" t="s">
+        <v>14</v>
+      </c>
+      <c r="C34" t="s">
+        <v>15</v>
+      </c>
+      <c r="D34" t="s">
+        <v>176</v>
+      </c>
+      <c r="E34" t="s">
+        <v>177</v>
+      </c>
+      <c r="F34" t="s">
+        <v>18</v>
+      </c>
+      <c r="G34" t="s">
+        <v>178</v>
+      </c>
+      <c r="H34" t="s">
+        <v>179</v>
+      </c>
+      <c r="I34" t="s">
+        <v>180</v>
+      </c>
+      <c r="J34" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="A35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B35" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35" t="s">
+        <v>15</v>
+      </c>
+      <c r="D35" t="s">
+        <v>84</v>
+      </c>
+      <c r="E35" t="s">
+        <v>182</v>
+      </c>
+      <c r="F35" t="s">
+        <v>18</v>
+      </c>
+      <c r="G35" t="s">
+        <v>183</v>
+      </c>
+      <c r="H35" t="s">
+        <v>168</v>
+      </c>
+      <c r="I35" t="s">
+        <v>184</v>
+      </c>
+      <c r="J35" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36" t="s">
+        <v>13</v>
+      </c>
+      <c r="B36" t="s">
+        <v>14</v>
+      </c>
+      <c r="C36" t="s">
+        <v>15</v>
+      </c>
+      <c r="D36" t="s">
+        <v>116</v>
+      </c>
+      <c r="E36" t="s">
+        <v>186</v>
+      </c>
+      <c r="F36" t="s">
+        <v>18</v>
+      </c>
+      <c r="G36" t="s">
         <v>71</v>
       </c>
-      <c r="B15" t="s">
-        <v>72</v>
-      </c>
-      <c r="C15" t="s">
-        <v>12</v>
-      </c>
-      <c r="D15" t="s">
-        <v>41</v>
-      </c>
-      <c r="E15" t="s">
-        <v>73</v>
-      </c>
-      <c r="F15" t="s">
-        <v>74</v>
-      </c>
-      <c r="G15" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" t="s">
-        <v>76</v>
-      </c>
-      <c r="B16" t="s">
-        <v>77</v>
-      </c>
-      <c r="C16" t="s">
-        <v>12</v>
-      </c>
-      <c r="D16" t="s">
-        <v>78</v>
-      </c>
-      <c r="E16" t="s">
-        <v>79</v>
-      </c>
-      <c r="F16" t="s">
-        <v>80</v>
-      </c>
-      <c r="G16" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" t="s">
-        <v>82</v>
-      </c>
-      <c r="B17" t="s">
-        <v>83</v>
-      </c>
-      <c r="C17" t="s">
-        <v>12</v>
-      </c>
-      <c r="D17" t="s">
-        <v>65</v>
-      </c>
-      <c r="E17" t="s">
-        <v>84</v>
-      </c>
-      <c r="F17" t="s">
-        <v>85</v>
-      </c>
-      <c r="G17" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" t="s">
-        <v>87</v>
-      </c>
-      <c r="B18" t="s">
-        <v>88</v>
-      </c>
-      <c r="C18" t="s">
-        <v>12</v>
-      </c>
-      <c r="D18" t="s">
-        <v>89</v>
-      </c>
-      <c r="E18" t="s">
-        <v>90</v>
-      </c>
-      <c r="F18" t="s">
-        <v>91</v>
-      </c>
-      <c r="G18" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" t="s">
-        <v>93</v>
-      </c>
-      <c r="B19" t="s">
-        <v>94</v>
-      </c>
-      <c r="C19" t="s">
-        <v>12</v>
-      </c>
-      <c r="D19" t="s">
-        <v>78</v>
-      </c>
-      <c r="E19" t="s">
-        <v>95</v>
-      </c>
-      <c r="F19" t="s">
-        <v>96</v>
-      </c>
-      <c r="G19" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" t="s">
-        <v>61</v>
-      </c>
-      <c r="B20" t="s">
-        <v>98</v>
-      </c>
-      <c r="C20" t="s">
-        <v>12</v>
-      </c>
-      <c r="D20" t="s">
-        <v>93</v>
-      </c>
-      <c r="E20" t="s">
-        <v>99</v>
-      </c>
-      <c r="F20" t="s">
-        <v>100</v>
-      </c>
-      <c r="G20" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" t="s">
-        <v>102</v>
-      </c>
-      <c r="B21" t="s">
-        <v>103</v>
-      </c>
-      <c r="C21" t="s">
-        <v>12</v>
-      </c>
-      <c r="D21" t="s">
-        <v>104</v>
-      </c>
-      <c r="E21" t="s">
-        <v>105</v>
-      </c>
-      <c r="F21" t="s">
-        <v>106</v>
-      </c>
-      <c r="G21" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" t="s">
-        <v>108</v>
-      </c>
-      <c r="B22" t="s">
-        <v>109</v>
-      </c>
-      <c r="C22" t="s">
-        <v>12</v>
-      </c>
-      <c r="D22" t="s">
-        <v>110</v>
-      </c>
-      <c r="E22" t="s">
-        <v>111</v>
-      </c>
-      <c r="F22" t="s">
-        <v>112</v>
-      </c>
-      <c r="G22" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" t="s">
-        <v>114</v>
-      </c>
-      <c r="B23" t="s">
-        <v>115</v>
-      </c>
-      <c r="C23" t="s">
-        <v>12</v>
-      </c>
-      <c r="D23" t="s">
-        <v>76</v>
-      </c>
-      <c r="E23" t="s">
-        <v>32</v>
-      </c>
-      <c r="F23" t="s">
-        <v>116</v>
-      </c>
-      <c r="G23" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" t="s">
-        <v>118</v>
-      </c>
-      <c r="B24" t="s">
-        <v>119</v>
-      </c>
-      <c r="C24" t="s">
-        <v>12</v>
-      </c>
-      <c r="D24" t="s">
-        <v>120</v>
-      </c>
-      <c r="E24" t="s">
-        <v>121</v>
-      </c>
-      <c r="F24" t="s">
-        <v>122</v>
-      </c>
-      <c r="G24" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25" t="s">
-        <v>13</v>
-      </c>
-      <c r="B25" t="s">
-        <v>124</v>
-      </c>
-      <c r="C25" t="s">
-        <v>12</v>
-      </c>
-      <c r="D25" t="s">
-        <v>93</v>
-      </c>
-      <c r="E25" t="s">
-        <v>125</v>
-      </c>
-      <c r="F25" t="s">
-        <v>126</v>
-      </c>
-      <c r="G25" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26" t="s">
-        <v>128</v>
-      </c>
-      <c r="B26" t="s">
-        <v>129</v>
-      </c>
-      <c r="C26" t="s">
-        <v>12</v>
-      </c>
-      <c r="D26" t="s">
-        <v>130</v>
-      </c>
-      <c r="E26" t="s">
-        <v>131</v>
-      </c>
-      <c r="F26" t="s">
-        <v>132</v>
-      </c>
-      <c r="G26" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27" t="s">
-        <v>134</v>
-      </c>
-      <c r="B27" t="s">
-        <v>135</v>
-      </c>
-      <c r="C27" t="s">
-        <v>12</v>
-      </c>
-      <c r="D27" t="s">
-        <v>65</v>
-      </c>
-      <c r="E27" t="s">
-        <v>136</v>
-      </c>
-      <c r="F27" t="s">
-        <v>137</v>
-      </c>
-      <c r="G27" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28" t="s">
-        <v>139</v>
-      </c>
-      <c r="B28" t="s">
-        <v>140</v>
-      </c>
-      <c r="C28" t="s">
-        <v>12</v>
-      </c>
-      <c r="D28" t="s">
-        <v>35</v>
-      </c>
-      <c r="E28" t="s">
-        <v>141</v>
-      </c>
-      <c r="F28" t="s">
-        <v>142</v>
-      </c>
-      <c r="G28" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29" t="s">
-        <v>144</v>
-      </c>
-      <c r="B29" t="s">
-        <v>145</v>
-      </c>
-      <c r="C29" t="s">
-        <v>12</v>
-      </c>
-      <c r="D29" t="s">
-        <v>93</v>
-      </c>
-      <c r="E29" t="s">
-        <v>146</v>
-      </c>
-      <c r="F29" t="s">
-        <v>147</v>
-      </c>
-      <c r="G29" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30" t="s">
-        <v>149</v>
-      </c>
-      <c r="B30" t="s">
-        <v>150</v>
-      </c>
-      <c r="C30" t="s">
-        <v>12</v>
-      </c>
-      <c r="D30" t="s">
-        <v>93</v>
-      </c>
-      <c r="E30" t="s">
-        <v>151</v>
-      </c>
-      <c r="F30" t="s">
-        <v>152</v>
-      </c>
-      <c r="G30" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31" t="s">
-        <v>55</v>
-      </c>
-      <c r="B31" t="s">
-        <v>154</v>
-      </c>
-      <c r="C31" t="s">
-        <v>12</v>
-      </c>
-      <c r="D31" t="s">
-        <v>155</v>
-      </c>
-      <c r="E31"/>
-      <c r="F31"/>
-      <c r="G31" t="s">
-        <v>156</v>
+      <c r="H36" t="s">
+        <v>187</v>
+      </c>
+      <c r="I36" t="s">
+        <v>188</v>
+      </c>
+      <c r="J36" t="s">
+        <v>189</v>
       </c>
     </row>
   </sheetData>
